--- a/Data/copper_price.xlsx
+++ b/Data/copper_price.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm"/>
     <numFmt numFmtId="165" formatCode="yyyy-m"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -38,6 +38,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -54,7 +58,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -66,6 +70,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3764,6 +3774,14 @@
         <v>10966.9</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="B436" s="5">
+        <v>10812.7</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
